--- a/exports/exhibit-collaborative.xlsx
+++ b/exports/exhibit-collaborative.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CCC Collaborative vs. Local Exh" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCC Collaborative vs. Local Exh" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/exhibit-collaborative.xlsx
+++ b/exports/exhibit-collaborative.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCC Collaborative vs. Local Exh" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CCC Collaborative vs. Local Exh" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9434</v>
+        <v>9619</v>
       </c>
       <c r="C2" t="n">
-        <v>3299</v>
+        <v>3379</v>
       </c>
       <c r="D2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E2" t="n">
         <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>87.7</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="C3" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E3" t="n">
         <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="4">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>169</v>
+        <v>220</v>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
         <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10760</v>
+        <v>11004</v>
       </c>
       <c r="C5" t="n">
-        <v>3451</v>
+        <v>3535</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
